--- a/Team-Data/2008-09/2-8-2008-09.xlsx
+++ b/Team-Data/2008-09/2-8-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,10 +806,10 @@
         <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF2" t="n">
         <v>11</v>
@@ -751,7 +818,7 @@
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
         <v>24</v>
@@ -760,7 +827,7 @@
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL2" t="n">
         <v>6</v>
@@ -769,16 +836,16 @@
         <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR2" t="n">
         <v>23</v>
@@ -799,7 +866,7 @@
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -811,7 +878,7 @@
         <v>18</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -846,82 +913,82 @@
         <v>52</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>0.788</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77.5</v>
+        <v>77.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.485</v>
+        <v>0.484</v>
       </c>
       <c r="L3" t="n">
         <v>6.6</v>
       </c>
       <c r="M3" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.392</v>
+        <v>0.39</v>
       </c>
       <c r="O3" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="P3" t="n">
-        <v>25.8</v>
+        <v>26.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.777</v>
+        <v>0.773</v>
       </c>
       <c r="R3" t="n">
         <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T3" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="V3" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W3" t="n">
         <v>8.4</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y3" t="n">
         <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.8</v>
+        <v>101.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -951,19 +1018,19 @@
         <v>19</v>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS3" t="n">
         <v>4</v>
@@ -975,7 +1042,7 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -1025,76 +1092,76 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E4" t="n">
         <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>0.38</v>
+        <v>0.388</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="J4" t="n">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="K4" t="n">
         <v>0.448</v>
       </c>
       <c r="L4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M4" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.361</v>
+        <v>0.358</v>
       </c>
       <c r="O4" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="P4" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.741</v>
+        <v>0.743</v>
       </c>
       <c r="R4" t="n">
         <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="T4" t="n">
-        <v>38.9</v>
+        <v>39.1</v>
       </c>
       <c r="U4" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V4" t="n">
         <v>15.6</v>
       </c>
       <c r="W4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y4" t="n">
         <v>6.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AB4" t="n">
         <v>91.90000000000001</v>
@@ -1103,7 +1170,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1124,34 +1191,34 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM4" t="n">
         <v>25</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
         <v>23</v>
       </c>
       <c r="AP4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ4" t="n">
         <v>27</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
       </c>
       <c r="AT4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AU4" t="n">
         <v>15</v>
@@ -1160,7 +1227,7 @@
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
         <v>18</v>
@@ -1169,7 +1236,7 @@
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA4" t="n">
         <v>13</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
         <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>0.42</v>
+        <v>0.431</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
@@ -1225,46 +1292,46 @@
         <v>37.8</v>
       </c>
       <c r="J5" t="n">
-        <v>84.3</v>
+        <v>84</v>
       </c>
       <c r="K5" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L5" t="n">
         <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N5" t="n">
         <v>0.376</v>
       </c>
       <c r="O5" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="P5" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S5" t="n">
         <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X5" t="n">
         <v>5.7</v>
@@ -1273,19 +1340,19 @@
         <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.1</v>
+        <v>100.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.2</v>
+        <v>-1.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>19</v>
@@ -1297,7 +1364,7 @@
         <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1306,7 +1373,7 @@
         <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
         <v>19</v>
@@ -1315,13 +1382,13 @@
         <v>22</v>
       </c>
       <c r="AN5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
         <v>9</v>
@@ -1330,13 +1397,13 @@
         <v>7</v>
       </c>
       <c r="AS5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV5" t="n">
         <v>19</v>
@@ -1351,16 +1418,16 @@
         <v>28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -1404,70 +1471,70 @@
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J6" t="n">
-        <v>78.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.474</v>
+        <v>0.475</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.385</v>
+        <v>0.381</v>
       </c>
       <c r="O6" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="P6" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.753</v>
+        <v>0.754</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="S6" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T6" t="n">
         <v>41.7</v>
       </c>
       <c r="U6" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="V6" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="W6" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X6" t="n">
         <v>5.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.2</v>
+        <v>101</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
@@ -1485,22 +1552,22 @@
         <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
         <v>5</v>
       </c>
       <c r="AN6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP6" t="n">
         <v>16</v>
@@ -1509,7 +1576,7 @@
         <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1521,10 +1588,10 @@
         <v>20</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
         <v>5</v>
@@ -1533,7 +1600,7 @@
         <v>4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
         <v>21</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1664,7 +1731,7 @@
         <v>14</v>
       </c>
       <c r="AI7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ7" t="n">
         <v>7</v>
@@ -1694,19 +1761,19 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>5</v>
       </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
         <v>7</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1861,7 +1928,7 @@
         <v>16</v>
       </c>
       <c r="AN8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,7 +1940,7 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
         <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>0.551</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1953,19 +2020,19 @@
         <v>35.9</v>
       </c>
       <c r="J9" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L9" t="n">
         <v>4.7</v>
       </c>
       <c r="M9" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.348</v>
+        <v>0.347</v>
       </c>
       <c r="O9" t="n">
         <v>17.1</v>
@@ -1974,55 +2041,55 @@
         <v>22.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.748</v>
+        <v>0.747</v>
       </c>
       <c r="R9" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S9" t="n">
         <v>29.8</v>
       </c>
       <c r="T9" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="U9" t="n">
         <v>20.2</v>
       </c>
       <c r="V9" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y9" t="n">
         <v>4</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG9" t="n">
         <v>13</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>14</v>
       </c>
       <c r="AH9" t="n">
         <v>12</v>
@@ -2046,16 +2113,16 @@
         <v>23</v>
       </c>
       <c r="AO9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS9" t="n">
         <v>17</v>
@@ -2064,7 +2131,7 @@
         <v>21</v>
       </c>
       <c r="AU9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2073,7 +2140,7 @@
         <v>27</v>
       </c>
       <c r="AX9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY9" t="n">
         <v>5</v>
@@ -2082,13 +2149,13 @@
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -2117,88 +2184,88 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
         <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>0.327</v>
+        <v>0.314</v>
       </c>
       <c r="H10" t="n">
         <v>48.7</v>
       </c>
       <c r="I10" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J10" t="n">
-        <v>85.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L10" t="n">
         <v>6.5</v>
       </c>
       <c r="M10" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.366</v>
+        <v>0.364</v>
       </c>
       <c r="O10" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="P10" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.772</v>
+        <v>0.771</v>
       </c>
       <c r="R10" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S10" t="n">
         <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U10" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V10" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X10" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z10" t="n">
         <v>22.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>106.8</v>
+        <v>106.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.1</v>
+        <v>-4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF10" t="n">
         <v>25</v>
@@ -2240,16 +2307,16 @@
         <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
         <v>16</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
         <v>7</v>
@@ -2258,13 +2325,13 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2398,7 +2465,7 @@
         <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
         <v>9</v>
@@ -2419,10 +2486,10 @@
         <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -2452,7 +2519,7 @@
         <v>19</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12" t="n">
         <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" t="n">
-        <v>0.385</v>
+        <v>0.392</v>
       </c>
       <c r="H12" t="n">
         <v>48.6</v>
@@ -2499,37 +2566,37 @@
         <v>38.9</v>
       </c>
       <c r="J12" t="n">
-        <v>86</v>
+        <v>86.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M12" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N12" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O12" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="P12" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T12" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="U12" t="n">
         <v>22.7</v>
@@ -2541,7 +2608,7 @@
         <v>7</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y12" t="n">
         <v>5.4</v>
@@ -2550,16 +2617,16 @@
         <v>23.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.9</v>
+        <v>104.7</v>
       </c>
       <c r="AC12" t="n">
         <v>-2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2571,7 +2638,7 @@
         <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI12" t="n">
         <v>3</v>
@@ -2592,10 +2659,10 @@
         <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ12" t="n">
         <v>4</v>
@@ -2604,10 +2671,10 @@
         <v>14</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
         <v>5</v>
@@ -2616,7 +2683,7 @@
         <v>22</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2625,16 +2692,16 @@
         <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
         <v>4</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>-7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF13" t="n">
         <v>28</v>
@@ -2771,13 +2838,13 @@
         <v>17</v>
       </c>
       <c r="AN13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP13" t="n">
         <v>25</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>26</v>
       </c>
       <c r="AQ13" t="n">
         <v>22</v>
@@ -2813,7 +2880,7 @@
         <v>26</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -2860,55 +2927,55 @@
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="J14" t="n">
-        <v>84.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.48</v>
+        <v>0.479</v>
       </c>
       <c r="L14" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.371</v>
+        <v>0.379</v>
       </c>
       <c r="O14" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="P14" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R14" t="n">
         <v>12.3</v>
       </c>
       <c r="S14" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T14" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="V14" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="W14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X14" t="n">
         <v>5.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z14" t="n">
         <v>20.2</v>
@@ -2917,13 +2984,13 @@
         <v>23</v>
       </c>
       <c r="AB14" t="n">
-        <v>109</v>
+        <v>108.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2953,10 +3020,10 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AO14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
         <v>5</v>
@@ -2968,7 +3035,7 @@
         <v>4</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2977,7 +3044,7 @@
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
         <v>4</v>
@@ -2989,7 +3056,7 @@
         <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA14" t="n">
         <v>4</v>
@@ -2998,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,7 +3184,7 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="n">
         <v>29</v>
@@ -3126,7 +3193,7 @@
         <v>28</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL15" t="n">
         <v>28</v>
@@ -3138,10 +3205,10 @@
         <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
         <v>24</v>
@@ -3153,7 +3220,7 @@
         <v>26</v>
       </c>
       <c r="AT15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
@@ -3174,7 +3241,7 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
         <v>29</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" t="n">
         <v>23</v>
       </c>
       <c r="G16" t="n">
-        <v>0.54</v>
+        <v>0.531</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J16" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="L16" t="n">
         <v>6.9</v>
@@ -3239,46 +3306,46 @@
         <v>19.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O16" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.739</v>
+        <v>0.742</v>
       </c>
       <c r="R16" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S16" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T16" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="U16" t="n">
         <v>19.9</v>
       </c>
       <c r="V16" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="W16" t="n">
         <v>8.1</v>
       </c>
       <c r="X16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB16" t="n">
         <v>96.59999999999999</v>
@@ -3287,28 +3354,28 @@
         <v>0.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG16" t="n">
         <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ16" t="n">
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
@@ -3320,19 +3387,19 @@
         <v>20</v>
       </c>
       <c r="AO16" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR16" t="n">
         <v>24</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT16" t="n">
         <v>25</v>
@@ -3350,10 +3417,10 @@
         <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
         <v>25</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E17" t="n">
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.462</v>
+        <v>0.453</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3421,31 +3488,31 @@
         <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O17" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="P17" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="R17" t="n">
         <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="U17" t="n">
         <v>21.2</v>
       </c>
       <c r="V17" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W17" t="n">
         <v>7.1</v>
@@ -3457,55 +3524,55 @@
         <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
       </c>
       <c r="AF17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH17" t="n">
         <v>17</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>17</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>18</v>
       </c>
       <c r="AJ17" t="n">
         <v>12</v>
       </c>
       <c r="AK17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL17" t="n">
         <v>23</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>24</v>
       </c>
       <c r="AM17" t="n">
         <v>23</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
         <v>8</v>
@@ -3514,19 +3581,19 @@
         <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT17" t="n">
         <v>15</v>
       </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
         <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3535,16 +3602,16 @@
         <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB17" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC17" t="n">
         <v>17</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>16</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G18" t="n">
-        <v>0.34</v>
+        <v>0.347</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3600,28 +3667,28 @@
         <v>5.9</v>
       </c>
       <c r="M18" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="O18" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P18" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R18" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S18" t="n">
         <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U18" t="n">
         <v>20.5</v>
@@ -3630,7 +3697,7 @@
         <v>14.3</v>
       </c>
       <c r="W18" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X18" t="n">
         <v>4.2</v>
@@ -3639,7 +3706,7 @@
         <v>6.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA18" t="n">
         <v>20.5</v>
@@ -3651,7 +3718,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>24</v>
@@ -3684,10 +3751,10 @@
         <v>26</v>
       </c>
       <c r="AO18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP18" t="n">
         <v>18</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>17</v>
       </c>
       <c r="AQ18" t="n">
         <v>15</v>
@@ -3696,10 +3763,10 @@
         <v>3</v>
       </c>
       <c r="AS18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU18" t="n">
         <v>18</v>
@@ -3723,7 +3790,7 @@
         <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC18" t="n">
         <v>24</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
-        <v>0.462</v>
+        <v>0.471</v>
       </c>
       <c r="H19" t="n">
         <v>48.6</v>
@@ -3773,37 +3840,37 @@
         <v>35.5</v>
       </c>
       <c r="J19" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M19" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="N19" t="n">
         <v>0.381</v>
       </c>
       <c r="O19" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="P19" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R19" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S19" t="n">
         <v>29.7</v>
       </c>
       <c r="T19" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U19" t="n">
         <v>19.5</v>
@@ -3818,22 +3885,22 @@
         <v>4.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.3</v>
+        <v>98.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>-1.6</v>
+        <v>-1.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE19" t="n">
         <v>17</v>
@@ -3845,16 +3912,16 @@
         <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI19" t="n">
         <v>27</v>
       </c>
       <c r="AJ19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>5</v>
@@ -3863,37 +3930,37 @@
         <v>6</v>
       </c>
       <c r="AN19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
         <v>12</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT19" t="n">
         <v>18</v>
       </c>
       <c r="AU19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY19" t="n">
         <v>17</v>
@@ -3902,10 +3969,10 @@
         <v>26</v>
       </c>
       <c r="BA19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB19" t="n">
         <v>17</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>18</v>
       </c>
       <c r="BC19" t="n">
         <v>18</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F20" t="n">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.625</v>
+        <v>0.617</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
@@ -3955,43 +4022,43 @@
         <v>34.9</v>
       </c>
       <c r="J20" t="n">
-        <v>76.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M20" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.388</v>
+        <v>0.391</v>
       </c>
       <c r="O20" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="P20" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="Q20" t="n">
         <v>0.8129999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S20" t="n">
         <v>28.9</v>
       </c>
       <c r="T20" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="U20" t="n">
         <v>19.8</v>
       </c>
       <c r="V20" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="W20" t="n">
         <v>7.6</v>
@@ -4006,25 +4073,25 @@
         <v>20.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB20" t="n">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC20" t="n">
         <v>2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF20" t="n">
         <v>7</v>
       </c>
       <c r="AG20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
@@ -4036,7 +4103,7 @@
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>8</v>
@@ -4045,13 +4112,13 @@
         <v>10</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP20" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
@@ -4063,16 +4130,16 @@
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU20" t="n">
         <v>27</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
         <v>23</v>
@@ -4081,16 +4148,16 @@
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E21" t="n">
         <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G21" t="n">
-        <v>0.42</v>
+        <v>0.429</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
@@ -4137,40 +4204,40 @@
         <v>37.9</v>
       </c>
       <c r="J21" t="n">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L21" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="M21" t="n">
         <v>28.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O21" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P21" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.802</v>
+        <v>0.8</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T21" t="n">
-        <v>42.3</v>
+        <v>42.6</v>
       </c>
       <c r="U21" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V21" t="n">
         <v>15</v>
@@ -4182,34 +4249,34 @@
         <v>2.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA21" t="n">
         <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
@@ -4227,31 +4294,31 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ21" t="n">
         <v>7</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT21" t="n">
         <v>9</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AU21" t="n">
         <v>10</v>
       </c>
-      <c r="AU21" t="n">
-        <v>9</v>
-      </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW21" t="n">
         <v>14</v>
@@ -4260,10 +4327,10 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
         <v>38</v>
       </c>
       <c r="G22" t="n">
-        <v>0.255</v>
+        <v>0.24</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J22" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.452</v>
+        <v>0.45</v>
       </c>
       <c r="L22" t="n">
         <v>4</v>
@@ -4334,7 +4401,7 @@
         <v>0.373</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P22" t="n">
         <v>25.9</v>
@@ -4352,10 +4419,10 @@
         <v>43.1</v>
       </c>
       <c r="U22" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="W22" t="n">
         <v>6.8</v>
@@ -4367,19 +4434,19 @@
         <v>5.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB22" t="n">
-        <v>97.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>-5.6</v>
+        <v>-5.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4391,16 +4458,16 @@
         <v>27</v>
       </c>
       <c r="AH22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI22" t="n">
         <v>15</v>
       </c>
-      <c r="AI22" t="n">
-        <v>14</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4409,13 +4476,13 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO22" t="n">
         <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
         <v>13</v>
@@ -4439,7 +4506,7 @@
         <v>23</v>
       </c>
       <c r="AX22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E23" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F23" t="n">
         <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>0.76</v>
+        <v>0.755</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
@@ -4501,31 +4568,31 @@
         <v>36.4</v>
       </c>
       <c r="J23" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K23" t="n">
         <v>0.463</v>
       </c>
       <c r="L23" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="M23" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.399</v>
+        <v>0.4</v>
       </c>
       <c r="O23" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="P23" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.721</v>
+        <v>0.722</v>
       </c>
       <c r="R23" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S23" t="n">
         <v>33.2</v>
@@ -4534,7 +4601,7 @@
         <v>43.2</v>
       </c>
       <c r="U23" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="V23" t="n">
         <v>13.9</v>
@@ -4543,7 +4610,7 @@
         <v>7.1</v>
       </c>
       <c r="X23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y23" t="n">
         <v>3.8</v>
@@ -4555,13 +4622,13 @@
         <v>22.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.8</v>
+        <v>102.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>16</v>
@@ -4582,7 +4649,7 @@
         <v>20</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4594,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP23" t="n">
         <v>6</v>
@@ -4609,10 +4676,10 @@
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV23" t="n">
         <v>13</v>
@@ -4636,7 +4703,7 @@
         <v>7</v>
       </c>
       <c r="BC23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE24" t="n">
         <v>16</v>
@@ -4758,10 +4825,10 @@
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK24" t="n">
         <v>11</v>
@@ -4773,13 +4840,13 @@
         <v>29</v>
       </c>
       <c r="AN24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ24" t="n">
         <v>26</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F25" t="n">
         <v>21</v>
       </c>
       <c r="G25" t="n">
-        <v>0.571</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,43 +4932,43 @@
         <v>38.7</v>
       </c>
       <c r="J25" t="n">
-        <v>78.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>0.496</v>
       </c>
       <c r="L25" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M25" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="O25" t="n">
         <v>21</v>
       </c>
       <c r="P25" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T25" t="n">
         <v>41.6</v>
       </c>
       <c r="U25" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V25" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W25" t="n">
         <v>6.4</v>
@@ -4910,7 +4977,7 @@
         <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z25" t="n">
         <v>20.5</v>
@@ -4922,10 +4989,10 @@
         <v>104.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4934,7 +5001,7 @@
         <v>11</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
         <v>22</v>
@@ -4949,22 +5016,22 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM25" t="n">
         <v>20</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP25" t="n">
         <v>4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
         <v>27</v>
@@ -4976,22 +5043,22 @@
         <v>14</v>
       </c>
       <c r="AU25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA25" t="n">
         <v>7</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -5032,40 +5099,40 @@
         <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>0.633</v>
+        <v>0.612</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.4</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.46</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
       </c>
       <c r="M26" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O26" t="n">
         <v>19.1</v>
       </c>
-      <c r="N26" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="O26" t="n">
-        <v>19.2</v>
-      </c>
       <c r="P26" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="Q26" t="n">
         <v>0.763</v>
@@ -5080,7 +5147,7 @@
         <v>40.8</v>
       </c>
       <c r="U26" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V26" t="n">
         <v>12.9</v>
@@ -5089,46 +5156,46 @@
         <v>6.9</v>
       </c>
       <c r="X26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
         <v>21</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AJ26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5137,13 +5204,13 @@
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
         <v>16</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
         <v>18</v>
@@ -5158,7 +5225,7 @@
         <v>19</v>
       </c>
       <c r="AU26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AV26" t="n">
         <v>6</v>
@@ -5167,7 +5234,7 @@
         <v>22</v>
       </c>
       <c r="AX26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AY26" t="n">
         <v>2</v>
@@ -5176,10 +5243,10 @@
         <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -5211,61 +5278,61 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E27" t="n">
         <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G27" t="n">
-        <v>0.212</v>
+        <v>0.216</v>
       </c>
       <c r="H27" t="n">
         <v>48.7</v>
       </c>
       <c r="I27" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J27" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.445</v>
+        <v>0.443</v>
       </c>
       <c r="L27" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M27" t="n">
         <v>18.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.355</v>
+        <v>0.349</v>
       </c>
       <c r="O27" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="P27" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0.805</v>
       </c>
       <c r="R27" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S27" t="n">
         <v>28.5</v>
       </c>
       <c r="T27" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="U27" t="n">
         <v>20</v>
       </c>
       <c r="V27" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W27" t="n">
         <v>6.8</v>
@@ -5280,58 +5347,58 @@
         <v>24</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-9.6</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
         <v>29</v>
       </c>
       <c r="AF27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
       </c>
       <c r="AJ27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM27" t="n">
         <v>14</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
         <v>6</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS27" t="n">
         <v>27</v>
@@ -5358,7 +5425,7 @@
         <v>30</v>
       </c>
       <c r="BA27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB27" t="n">
         <v>13</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F28" t="n">
         <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>0.694</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J28" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L28" t="n">
         <v>8</v>
@@ -5423,16 +5490,16 @@
         <v>20.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.391</v>
+        <v>0.392</v>
       </c>
       <c r="O28" t="n">
         <v>15.8</v>
       </c>
       <c r="P28" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.766</v>
+        <v>0.763</v>
       </c>
       <c r="R28" t="n">
         <v>8.699999999999999</v>
@@ -5453,10 +5520,10 @@
         <v>5.9</v>
       </c>
       <c r="X28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z28" t="n">
         <v>18.8</v>
@@ -5465,16 +5532,16 @@
         <v>18.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF28" t="n">
         <v>5</v>
@@ -5495,13 +5562,13 @@
         <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM28" t="n">
         <v>7</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5516,13 +5583,13 @@
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT28" t="n">
         <v>22</v>
       </c>
       <c r="AU28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5750,13 @@
         <v>21</v>
       </c>
       <c r="AN29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO29" t="n">
         <v>17</v>
       </c>
       <c r="AP29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5701,7 +5768,7 @@
         <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
         <v>8</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -5757,46 +5824,46 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
       </c>
       <c r="F30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.569</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J30" t="n">
         <v>79.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L30" t="n">
         <v>4.8</v>
       </c>
       <c r="M30" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="O30" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="P30" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R30" t="n">
         <v>11.9</v>
@@ -5808,13 +5875,13 @@
         <v>41.2</v>
       </c>
       <c r="U30" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="V30" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W30" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X30" t="n">
         <v>4.7</v>
@@ -5829,28 +5896,28 @@
         <v>23.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>102.4</v>
+        <v>102.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF30" t="n">
         <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH30" t="n">
         <v>16</v>
       </c>
       <c r="AI30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ30" t="n">
         <v>17</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5877,7 +5944,7 @@
         <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
         <v>22</v>
@@ -5889,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
@@ -5901,7 +5968,7 @@
         <v>16</v>
       </c>
       <c r="AZ30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA30" t="n">
         <v>1</v>
@@ -5910,7 +5977,7 @@
         <v>8</v>
       </c>
       <c r="BC30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
@@ -5939,61 +6006,61 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F31" t="n">
         <v>40</v>
       </c>
       <c r="G31" t="n">
-        <v>0.216</v>
+        <v>0.2</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J31" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M31" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.327</v>
+        <v>0.321</v>
       </c>
       <c r="O31" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="P31" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.761</v>
+        <v>0.759</v>
       </c>
       <c r="R31" t="n">
         <v>11.9</v>
       </c>
       <c r="S31" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="T31" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="U31" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V31" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W31" t="n">
         <v>7.5</v>
@@ -6002,37 +6069,37 @@
         <v>3.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>94.7</v>
+        <v>94.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.7</v>
+        <v>-7.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF31" t="n">
         <v>29</v>
       </c>
       <c r="AG31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
         <v>9</v>
@@ -6047,19 +6114,19 @@
         <v>24</v>
       </c>
       <c r="AN31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO31" t="n">
         <v>29</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>28</v>
       </c>
       <c r="AP31" t="n">
         <v>28</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS31" t="n">
         <v>29</v>
@@ -6083,13 +6150,13 @@
         <v>18</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA31" t="n">
         <v>28</v>
       </c>
       <c r="BB31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-8-2008-09</t>
+          <t>2009-02-08</t>
         </is>
       </c>
     </row>
